--- a/extenbooks/XS1101.xlsx
+++ b/extenbooks/XS1101.xlsx
@@ -1540,9 +1540,9 @@
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="53" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1583,17 +1583,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>S605, S604, BEA_NIPA</t>
+          <t>S605, S606, S604, S617</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>XS1101-COMBINED</t>
+          <t>XS1101-A</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>(B_w - T_w) / EC</t>
+          <t>XS1101 = (B_w - T_w)/EC = (S605 + S606 - S604)/S617</t>
         </is>
       </c>
     </row>

--- a/extenbooks/XS1101.xlsx
+++ b/extenbooks/XS1101.xlsx
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Registry construction formula: (B_w - T_w) / EC, inputs S605, S604, BEA_NIPA. This matches S&amp;T (1987) formula NT/AW = (B - T_w)/EC exactly. S605 carries benefits received by workers; S604 carries taxes paid by workers; BEA_NIPA provides employee compensation (EC/AW) denominator. The 1987 paper is the direct methodological source for the S605/S604 series construction in the ST2 project.</t>
+          <t>Registry construction formula: (B_w - T_w) / EC, inputs S605, S604, BEA_NIPA. This matches S&amp;T (1987) formula NT/AW = (B - T_w)/EC exactly. S605 carries benefits received by workers; S604 carries taxes paid by workers; BEA_NIPA provides employee compensation (EC/AW) denominator. The 1987 paper is the direct methodological source for the S605/S604 series construction in the predecessor-build project.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
